--- a/工单表.xlsx
+++ b/工单表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25002" windowHeight="17434" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级工单表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="真机工具检验" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="升级工单表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="真机工具检验" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -625,8 +625,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1076,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="25.7833333333333" customWidth="1" min="2" max="2"/>
@@ -1122,6 +1125,40 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>UPG-01</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>全量工具元数据补全：description/inputSchema/output 三件套</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr"/>
+      <c r="G2" s="1" t="inlineStr"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>方案: 设计师/方案设计/UPG-01_全量工具元数据补全_方案.md</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">

--- a/工单表.xlsx
+++ b/工单表.xlsx
@@ -1151,14 +1151,14 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>待派单</t>
+          <t>✅已派单(待领单)</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr"/>
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>方案: 设计师/方案设计/UPG-01_全量工具元数据补全_方案.md</t>
+          <t>方案: 设计师/方案设计/UPG-01_全量工具元数据补全_方案.md | 派单@2026-08-26 派单文本见工单库</t>
         </is>
       </c>
     </row>

--- a/工单表.xlsx
+++ b/工单表.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="25.7833333333333" customWidth="1" min="2" max="2"/>
@@ -1159,6 +1159,108 @@
       <c r="H2" s="1" t="inlineStr">
         <is>
           <t>方案: 设计师/方案设计/UPG-01_全量工具元数据补全_方案.md | 派单@2026-08-26 派单文本见工单库</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UPG-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>P0-A 设备类工具包迁移（AVD 内置 device.*/sensor.* 非敏感子集）</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>方案: 老版下线评估文件P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UPG-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P0-B 生活场景 MCP server（12306/地图/生活搜索，市场上架）</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>方案: 按 dev-docs.html + MCP_TOOL_DEV_GUIDE.md 实验</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UPG-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>P0-C Obsidian 工具包迁移（AVD 内置 obsidian.*）</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>方案: 老版 obsidian.* ×11 移植</t>
         </is>
       </c>
     </row>

--- a/工单表.xlsx
+++ b/工单表.xlsx
@@ -1188,8 +1188,6 @@
           <t>待派单</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>方案: 老版下线评估文件P0</t>
@@ -1204,7 +1202,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P0-B 生活场景 MCP server（12306/地图/生活搜索，市场上架）</t>
+          <t>P0-B 生活场景：12306 内置化已交付（scene.trainQuery/stationLookup）；地图待 key</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1219,14 +1217,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>待派单</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>✅ 完成</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>方案: 按 dev-docs.html + MCP_TOOL_DEV_GUIDE.md 实验</t>
+          <t>main bce578d（报告 DELIVERY_UPG03_12306场景工具_2026-08-26.md）| 12306 server 化被数据中心 IP 风控 → 挂账 | L3 AI 未回复待补</t>
         </is>
       </c>
     </row>
@@ -1256,8 +1252,6 @@
           <t>待派单</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>方案: 老版 obsidian.* ×11 移植</t>

--- a/工单表.xlsx
+++ b/工单表.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>方案: 老版下线评估文件P0</t>
+          <t>设计: 设计师/方案设计/UPG-02_设备类工具包_方案设计.md</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P0-B 生活场景：12306 内置化已交付（scene.trainQuery/stationLookup）；地图待 key</t>
+          <t>P0-B 生活场景工具（12306 内置 + 地图）</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>✅ 完成</t>
+          <t>待派单</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>main bce578d（报告 DELIVERY_UPG03_12306场景工具_2026-08-26.md）| 12306 server 化被数据中心 IP 风控 → 挂账 | L3 AI 未回复待补</t>
+          <t>设计: 设计师/方案设计/UPG-03_生活场景工具_方案设计.md | 实验代码 bce578d(SceneTools) 在 main，需程序员认领复核后正式交付</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>方案: 老版 obsidian.* ×11 移植</t>
+          <t>设计: 设计师/方案设计/UPG-04_Obsidian工具包_方案设计.md</t>
         </is>
       </c>
     </row>

--- a/工单表.xlsx
+++ b/工单表.xlsx
@@ -1079,7 +1079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="25.7833333333333" customWidth="1" min="2" max="2"/>
@@ -1255,6 +1255,108 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>设计: 设计师/方案设计/UPG-04_Obsidian工具包_方案设计.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UPG-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>记忆体系回补（基因化 + memory.* 工具接线 + 预算投影）</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>设计: 设计师/方案设计/UPG-05_记忆体系回补_方案设计.md | ⏳待专家审</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UPG-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>确定性防编造三件套（FabricateGuard/GoalGate/AcceptanceJudge）</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>设计: 设计师/方案设计/UPG-06_确定性防编造三件套_方案设计.md | ⏳待专家审</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UPG-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>计划授权 + 预算口径 + 设备能力裁剪</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>✅ 方案完成</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>待派单</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>设计: 设计师/方案设计/UPG-07_计划授权预算口径设备裁剪_方案设计.md | ⏳待专家审</t>
         </is>
       </c>
     </row>
